--- a/output/pdf_financials_xlsx/KLD.xlsx
+++ b/output/pdf_financials_xlsx/KLD.xlsx
@@ -3064,25 +3064,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.196</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.386513</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.635983</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.225248</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.548242</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.084156</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.985324</v>
       </c>
     </row>
     <row r="93">
@@ -3781,25 +3781,25 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.1</v>
+        <v>-0.08036699999999999</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.780829</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-18.703821</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-1.08606</v>
+        <v>-17.993594</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.054171</v>
+        <v>-22.724915</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1.032188</v>
+        <v>-15.490724</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>11.369601</v>
+        <v>-17.995131</v>
       </c>
     </row>
     <row r="119">
@@ -5220,7 +5220,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -5861,7 +5865,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -6907,7 +6915,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>0.196</v>
       </c>
@@ -7828,7 +7840,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>-0.180367</v>
       </c>
@@ -9260,7 +9276,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -10929,7 +10949,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KLD.xlsx
+++ b/output/pdf_financials_xlsx/KLD.xlsx
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         <v>-0.225085</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.225085</v>
+        <v>-0.225415</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.007599</v>
@@ -1250,7 +1250,7 @@
         <v>-0.225085</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.225085</v>
+        <v>-0.225415</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.040942</v>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.327993</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.449124</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>9.418796</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.327993</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.449124</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>9.418796</v>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.327993</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.463697</v>
+        <v>0.014573</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.113071</v>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">

--- a/output/pdf_financials_xlsx/KLD.xlsx
+++ b/output/pdf_financials_xlsx/KLD.xlsx
@@ -595,19 +595,19 @@
         <v>0.105689</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.260551</v>
+        <v>0.366984</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.206671</v>
+        <v>0.401298</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.198241</v>
+        <v>0.525139</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.249457</v>
+        <v>0.580728</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.223878</v>
+        <v>0.71368</v>
       </c>
     </row>
     <row r="8">
@@ -2248,25 +2248,25 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.167047</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.321551</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.907361</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.340778</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.831142</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.262195</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.363921</v>
       </c>
     </row>
     <row r="65">
@@ -2332,25 +2332,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.04121</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.741299</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.355865</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.48822</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.758285</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.683924</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.6191</v>
       </c>
     </row>
     <row r="68">
@@ -3594,16 +3594,16 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012928</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.041183</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004781</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007189</v>
       </c>
     </row>
     <row r="112">
@@ -3703,13 +3703,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.829117</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>8.954980000000001</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>7.214124</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012928</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.041183</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004781</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007189</v>
       </c>
     </row>
     <row r="135">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.137975</v>
+        <v>-0.179158</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>1.121405</v>
+        <v>1.116624</v>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
@@ -7452,7 +7452,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -7973,7 +7977,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -8110,7 +8118,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -9072,7 +9084,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -9427,7 +9443,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -9531,7 +9551,11 @@
           <t>Proceeds from sales of investments</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -9890,7 +9914,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -10096,7 +10124,11 @@
           <t>Proceeds from sales of investments</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -10898,7 +10930,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -12999,7 +13035,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -16463,7 +16503,11 @@
           <t>Deferred income tax recovery (expense) 18</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
